--- a/テンプレート.xlsx
+++ b/テンプレート.xlsx
@@ -686,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -956,6 +956,30 @@
       <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>自己資本</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>非支配株主持分</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
